--- a/inbox/mowbray_contacts.xlsx
+++ b/inbox/mowbray_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -537,6 +537,9 @@
       <c r="D5" t="s">
         <v>34</v>
       </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
@@ -551,6 +554,9 @@
       <c r="D6" t="s">
         <v>33</v>
       </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
@@ -565,6 +571,9 @@
       <c r="D7" t="s">
         <v>33</v>
       </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
@@ -579,6 +588,9 @@
       <c r="D8" t="s">
         <v>33</v>
       </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
@@ -593,6 +605,9 @@
       <c r="D9" t="s">
         <v>33</v>
       </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
@@ -607,6 +622,9 @@
       <c r="D10" t="s">
         <v>33</v>
       </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
@@ -620,6 +638,9 @@
       </c>
       <c r="D11" t="s">
         <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:5">

--- a/inbox/mowbray_contacts.xlsx
+++ b/inbox/mowbray_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -656,6 +656,9 @@
       <c r="D12" t="s">
         <v>33</v>
       </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
